--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_621_Madeira_Isl_Portugal.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_621_Madeira_Isl_Portugal.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R67c00b89a8574e07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9cd8e9b15f2f47a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra70d75fcb47846d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4882e30e4a864746"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4b6bbf2e57f54b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rcd1d500049a34312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0c5b52db223e4d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R96d70693608f43b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rffb3077f505b481f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R07e603355a8e4f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re389ebf6009d4dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R023e80b71f1d4b38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ621CommercialTable" displayName="EEZ621CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ621CommercialTable" displayName="EEZ621CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ621FunctionalTable" displayName="EEZ621FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ621FunctionalTable" displayName="EEZ621FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ621ValidationTable" displayName="EEZ621ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ621ValidationTable" displayName="EEZ621ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7260,7 +7214,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80c146ef352a4cfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fbcdc2ed7244868"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7270,20 +7224,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7291,660 +7235,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>16.472213966099996</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.249781151507781</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1777.3835300666465</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>16.472213966099996</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1777.6579775838065</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$99,A2,'Species'!$U$2:$U$99))</x:f>
-        <x:v>29281.962565305053</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.249781151507781</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1777.3835300666465</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>29277.441807079926</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>4.520758225127793</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0001544109712495</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00015441097124935875</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.81058541</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.0916170238284946</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>123.48580118790814</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.81058541</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>155.8248122211002</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$99,A3,'Species'!$U$2:$U$99))</x:f>
-        <x:v>126.3093193024135</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.0916170238284946</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>123.48580118790814</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>100.095788785079</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>26.213530517334505</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.261884449241106</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.26188444924110615</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.00006317229999999999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.3794892856520975</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>239.6013637688113</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.00006317229999999999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>247.62278084364144</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$99,A4,'Species'!$U$2:$U$99))</x:f>
-        <x:v>0.015642900598288767</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.3794892856520975</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>239.6013637688113</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>0.015136169232412476</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0.0005067313658762909</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0334781778728517</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.033478177872851754</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2.5897128999000003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.12283228763709</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>132.68819541384346</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2.5897128999000003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>134.60271155235557</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$99,A5,'Species'!$U$2:$U$99))</x:f>
-        <x:v>348.582378468654</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.12283228763709</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>132.68819541384346</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>343.62433132768246</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>4.95804714097153</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0144286847261799</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.01442868472617995</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>81.2204371858</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.099994076976231</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589082423513105</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>81.2204371858</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.58910134358759</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$99,A6,'Species'!$U$2:$U$99))</x:f>
-        <x:v>1022.4923149025261</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.099994076976231</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589082423513105</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1022.4907782058049</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.0015366967212457894</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0000015028954334</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.000001502895433386966</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>956.5330960289001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.290413141762558</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>195.17003578969508</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>956.5330960289001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>203.9860272854443</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$99,A7,'Species'!$U$2:$U$99))</x:f>
-        <x:v>195119.38622598173</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.290413141762558</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>195.17003578969508</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>186686.59858598828</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>8432.787639993447</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0451708248147726</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04517082481477258</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3087.2969189534</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.226841418855806</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1685.9372987438883</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3087.2969189534</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2311.4343116061987</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$99,A8,'Species'!$U$2:$U$99))</x:f>
-        <x:v>7136084.028584991</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.226841418855806</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1685.9372987438883</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>5204989.027960625</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1931095.000624366</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.371008467116979</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.37100846711697905</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>5.4622897641</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.69</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>489.77881936844614</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>5.4622897641</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>489.77881936844614</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$99,A9,'Species'!$U$2:$U$99))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2675.313831709246</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.69</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>489.77881936844614</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>2675.313831709246</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4.0157410446</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9192944295967957</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>830.4135549278913</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4.0157410446</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>830.6575037504347</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$99,A10,'Species'!$U$2:$U$99))</x:f>
-        <x:v>3335.7054318155992</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9192944295967957</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>830.4135549278913</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3334.72579651613</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0.9796352994694644</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.000293767871557</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.00029376787155720977</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>327.1062034653</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.330855020557797</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2142.1753646921916</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>327.1062034653</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2198.9069489237745</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$99,A11,'Species'!$U$2:$U$99))</x:f>
-        <x:v>719276.1038359222</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.330855020557797</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2142.1753646921916</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>700718.8507013572</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>18557.253134564962</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0264831652751896</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.026483165275189617</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>10446.6379190154</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.39820895925658</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2501.5486835029096</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>10446.6379190154</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2558.1240886769856</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$99,A12,'Species'!$U$2:$U$99))</x:f>
-        <x:v>26723796.106319714</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.39820895925658</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2501.5486835029096</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>26132773.33334455</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>591022.7729751654</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0226161519650514</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.022616151965051488</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5a2aaf4b91f4d8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb107a270e1cf499e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7954,20 +7469,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7975,1254 +7480,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6.875918990800001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.809438601753428</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>644.8201521764817</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6.875918990800001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>711.1994150073223</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$99,A2,'Species'!$U$2:$U$99))</x:f>
-        <x:v>4890.149563894698</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.809438601753428</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>644.8201521764817</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4433.731130000817</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>456.41843389388123</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1029422895776264</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.1029422895776265</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6.5994984877</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.767542850653542</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>585.5215052825844</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6.5994984877</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>643.2456749929919</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$99,A3,'Species'!$U$2:$U$99))</x:f>
-        <x:v>4245.098859335816</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.767542850653542</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>585.5215052825844</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3864.1482886282433</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>380.95057070757275</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0985859087832286</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.09858590878322857</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.1657267117</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.1657267117</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$99,A4,'Species'!$U$2:$U$99))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>362.5705399206112</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>362.5705399206112</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2248.5292803098</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.479958296501075</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>3019.6617408791453</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2248.5292803098</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>3019.6830793674485</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$99,A5,'Species'!$U$2:$U$99))</x:f>
-        <x:v>6789845.82121377</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.479958296501075</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>3019.6617408791453</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>6789797.840998023</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>47.98021574690938</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000070665160983</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00000706651609819606</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6.2539126337</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.058455160118013</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1144.0767504899504</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6.2539126337</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1283.8148786893971</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$99,A6,'Species'!$U$2:$U$99))</x:f>
-        <x:v>8028.866089167654</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.058455160118013</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1144.0767504899504</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>7154.956043811543</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>873.9100453561105</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1221405191038136</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.12214051910381361</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>10432.5667885844</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.398142755042674</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2501.167374394493</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>10432.5667885844</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2557.7518677366356</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$99,A7,'Species'!$U$2:$U$99))</x:f>
-        <x:v>26683917.188788943</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.398142755042674</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2501.167374394493</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>26093595.68279883</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>590321.5059901141</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0226232334234895</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.022623233423489434</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.2511048725</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8190759907496417</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>659.289244398266</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.2511048725</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>659.5788589004263</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$99,A8,'Species'!$U$2:$U$99))</x:f>
-        <x:v>165.62346526788707</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8190759907496417</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>659.289244398266</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>165.55074165524792</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0.07272361263915172</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0004392829165973</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0004392829165972293</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4.029059309</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9174035251313795</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>826.8058202031693</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4.029059309</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>828.383408092285</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$99,A9,'Species'!$U$2:$U$99))</x:f>
-        <x:v>3337.6058817953667</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9174035251313795</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>826.8058202031693</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3331.24968662496</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>6.356195170406863</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0019080512625418</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0019080512625418398</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>297.51479928840007</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.361942850721512</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2301.138988126995</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>297.51479928840007</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2313.7921777577235</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$99,A10,'Species'!$U$2:$U$99))</x:f>
-        <x:v>688387.4153606592</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.361942850721512</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2301.138988126995</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>684622.904187315</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3764.5111733442172</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.005498663790416</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.005498663790415979</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.2513005142</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.4259626661758737</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>266.6629419718367</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.2513005142</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>268.0534882554883</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$99,A11,'Species'!$U$2:$U$99))</x:f>
-        <x:v>67.36197943170787</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.4259626661758737</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>266.6629419718367</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>67.01253443560732</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0.34944499610054436</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0052146213994686</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0052146213994686</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.5763303094</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.1737058431444005</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1491.7836506348892</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.5763303094</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1552.2703624249605</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$99,A12,'Species'!$U$2:$U$99))</x:f>
-        <x:v>894.6204582488275</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.1737058431444005</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1491.7836506348892</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>859.7601329282671</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>34.86032532056038</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0405465710556143</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0405465710556143</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>7.0661833162</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>7.0661833162</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$99,A13,'Species'!$U$2:$U$99))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>8495.42088955419</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>8495.42088955419</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>459.83377112060003</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4248032858917092</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>265.9520154695275</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>459.83377112060003</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>335.80066820323606</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$99,A14,'Species'!$U$2:$U$99))</x:f>
-        <x:v>154412.4876047114</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4248032858917092</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>265.9520154695275</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>122293.71821047699</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>32118.76939423442</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2626362977937715</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.26263629779377157</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>940.0078423152002</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.2795423376336976</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>190.34537886359684</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>940.0078423152002</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>190.47367312340177</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$99,A15,'Species'!$U$2:$U$99))</x:f>
-        <x:v>179046.74649057962</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.2795423376336976</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>190.34537886359684</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>178926.14888023896</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>120.59761034065741</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0006740077461869</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.0006740077461868208</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>393.0401789986</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.739473426457413</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>548.87497010403</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>393.0401789986</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>628.449271894198</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$99,A16,'Species'!$U$2:$U$99))</x:f>
-        <x:v>247005.81431683543</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.739473426457413</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>548.87497010403</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>215729.9164975392</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>31275.897819296224</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1449771006593468</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.14497710065934682</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>0.21757164250000002</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.4498448201722787</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>281.73760613447456</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>0.21757164250000002</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>438.99721988700657</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$99,A17,'Species'!$U$2:$U$99))</x:f>
-        <x:v>95.51334618374969</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.4498448201722787</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>281.73760613447456</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>61.29811372069571</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>34.21523246305398</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.5581775749080204</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.5581775749080203</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>81.2230149568</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.100000444060123</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>12.589266990287104</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>81.2230149568</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>12.58933619170209</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$99,A18,'Species'!$U$2:$U$99))</x:f>
-        <x:v>1022.5438417948025</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.100000444060123</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>12.589266990287104</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1022.538221047238</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0.0056207475644214355</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0000054968581602</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.000005496858160142822</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>0.5592848958</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.9413872706680024</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>87.37501648019914</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>0.5592848958</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>105.39769679706347</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$99,A19,'Species'!$U$2:$U$99))</x:f>
-        <x:v>58.94733987070563</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.9413872706680024</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>87.37501648019914</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>48.86752698765145</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>10.079812883054181</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.20626811922775</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.20626811922775</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>2.5976522075</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.121881094301189</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>132.39789927100142</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>2.5976522075</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>133.23747956848612</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$99,A20,'Species'!$U$2:$U$99))</x:f>
-        <x:v>346.1046329228141</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.121881094301189</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>132.39789927100142</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>343.9236953096795</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>2.180937613134631</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0063413415326643</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.006341341532664238</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>10.6455989643</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>10.6455989643</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$99,A21,'Species'!$U$2:$U$99))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>5717.02513523533</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>5717.02513523533</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>0.00006317229999999999</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.3794892856520975</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>239.6013637688113</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>0.00006317229999999999</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>247.62278084364144</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$99,A22,'Species'!$U$2:$U$99))</x:f>
-        <x:v>0.015642900598288767</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.3794892856520975</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>239.6013637688113</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>0.015136169232412476</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0.0005067313658762909</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0334781778728517</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.033478177872851754</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>29.3402993044</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>4.02</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>1047.1285480508984</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>29.3402993044</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>1047.1285480508984</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$99,A23,'Species'!$U$2:$U$99))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>30723.065009995156</x:v>
       </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>4.02</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>1047.1285480508984</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>30723.065009995156</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53c4501a6c9d48cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33ac635b13154461"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9397,7 +8088,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9496,7 +8187,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>34811066.00645101</x:v>
+        <x:v>32261921.518062312</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9510,7 +8201,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>34811066.00645102</x:v>
+        <x:v>34151617.34439845</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9524,7 +8215,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-2549144.488388706</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9538,7 +8229,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-659448.6620525718</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9549,9 +8240,9 @@
         <x:v>EEZ_621</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9563,47 +8254,19 @@
         <x:v>EEZ_621</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_621</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_621</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b48cc42887e484f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd30ee07dd3cc4839"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9650,7 +8313,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
